--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/37.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/37.xlsx
@@ -426,13 +426,13 @@
         <v>-8.88434950918772</v>
       </c>
       <c r="E2">
-        <v>-19.39706385983247</v>
+        <v>-24.64648904341998</v>
       </c>
       <c r="F2">
-        <v>-5.372724024045475</v>
+        <v>-4.866749759108911</v>
       </c>
       <c r="G2">
-        <v>-12.62352511010178</v>
+        <v>-16.48495535874431</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.76760892823123</v>
       </c>
       <c r="E3">
-        <v>-19.54251391648483</v>
+        <v>-24.71716040878368</v>
       </c>
       <c r="F3">
-        <v>-5.274766265194821</v>
+        <v>-5.020532025601625</v>
       </c>
       <c r="G3">
-        <v>-12.89517523487222</v>
+        <v>-15.70615614172184</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.670476366952887</v>
       </c>
       <c r="E4">
-        <v>-19.56511553025711</v>
+        <v>-25.14707561717587</v>
       </c>
       <c r="F4">
-        <v>-5.546893240688488</v>
+        <v>-5.061049132007355</v>
       </c>
       <c r="G4">
-        <v>-12.93277641110726</v>
+        <v>-15.4425903691583</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.588613213012165</v>
       </c>
       <c r="E5">
-        <v>-20.61251534043921</v>
+        <v>-25.57869806026896</v>
       </c>
       <c r="F5">
-        <v>-5.353792515421895</v>
+        <v>-4.969555124000746</v>
       </c>
       <c r="G5">
-        <v>-12.73730193919545</v>
+        <v>-14.95130706640323</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.501015739258927</v>
       </c>
       <c r="E6">
-        <v>-20.08741160840578</v>
+        <v>-25.58833012448327</v>
       </c>
       <c r="F6">
-        <v>-5.2915075704054</v>
+        <v>-4.737378651609296</v>
       </c>
       <c r="G6">
-        <v>-11.9882281105701</v>
+        <v>-15.41866836709153</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.399860551205684</v>
       </c>
       <c r="E7">
-        <v>-20.51838195124176</v>
+        <v>-26.12154435346443</v>
       </c>
       <c r="F7">
-        <v>-5.096934836264032</v>
+        <v>-4.831921880025609</v>
       </c>
       <c r="G7">
-        <v>-12.40920701298044</v>
+        <v>-15.13008811243326</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.276580297814776</v>
       </c>
       <c r="E8">
-        <v>-20.86521777548923</v>
+        <v>-26.69435555916866</v>
       </c>
       <c r="F8">
-        <v>-4.913374418375481</v>
+        <v>-4.928669394100772</v>
       </c>
       <c r="G8">
-        <v>-13.13257445549335</v>
+        <v>-15.09214595000767</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.118816534359173</v>
       </c>
       <c r="E9">
-        <v>-22.30212522049308</v>
+        <v>-27.0925352217151</v>
       </c>
       <c r="F9">
-        <v>-4.963284382761555</v>
+        <v>-4.7342731022162</v>
       </c>
       <c r="G9">
-        <v>-12.60978965665934</v>
+        <v>-14.67367147529779</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.917580669403174</v>
       </c>
       <c r="E10">
-        <v>-21.17435405362285</v>
+        <v>-27.53794233968754</v>
       </c>
       <c r="F10">
-        <v>-5.160912135884447</v>
+        <v>-4.689785630848853</v>
       </c>
       <c r="G10">
-        <v>-11.3336504938177</v>
+        <v>-13.94645883414102</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.678055400634067</v>
       </c>
       <c r="E11">
-        <v>-23.10847435924688</v>
+        <v>-27.89143502072628</v>
       </c>
       <c r="F11">
-        <v>-5.360682875478381</v>
+        <v>-4.71059836184419</v>
       </c>
       <c r="G11">
-        <v>-12.44190527127182</v>
+        <v>-13.57635142975989</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.401833887203735</v>
       </c>
       <c r="E12">
-        <v>-23.27811552404821</v>
+        <v>-28.49051137567501</v>
       </c>
       <c r="F12">
-        <v>-4.213869505490273</v>
+        <v>-4.731102940165687</v>
       </c>
       <c r="G12">
-        <v>-11.75567883916399</v>
+        <v>-13.41074635497615</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.087635612268805</v>
       </c>
       <c r="E13">
-        <v>-23.98563977453263</v>
+        <v>-29.71032604098813</v>
       </c>
       <c r="F13">
-        <v>-4.404698018970986</v>
+        <v>-4.717605521704471</v>
       </c>
       <c r="G13">
-        <v>-11.33847726921396</v>
+        <v>-13.42112491524177</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.754511322276581</v>
       </c>
       <c r="E14">
-        <v>-24.88400750512228</v>
+        <v>-29.14581326390296</v>
       </c>
       <c r="F14">
-        <v>-4.634024907496807</v>
+        <v>-4.541464790642796</v>
       </c>
       <c r="G14">
-        <v>-11.90905641399843</v>
+        <v>-12.91749824344352</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.417033396306149</v>
       </c>
       <c r="E15">
-        <v>-25.35486011854382</v>
+        <v>-30.03577161826038</v>
       </c>
       <c r="F15">
-        <v>-4.65673294310975</v>
+        <v>-4.405011141849244</v>
       </c>
       <c r="G15">
-        <v>-11.18217979321389</v>
+        <v>-12.88054593413418</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.086560475060613</v>
       </c>
       <c r="E16">
-        <v>-25.53031584397101</v>
+        <v>-30.91459898350694</v>
       </c>
       <c r="F16">
-        <v>-4.198861973253754</v>
+        <v>-4.52685487475962</v>
       </c>
       <c r="G16">
-        <v>-10.56227683043982</v>
+        <v>-12.17089408179046</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.782223415247811</v>
       </c>
       <c r="E17">
-        <v>-26.05796457839674</v>
+        <v>-31.09977281415459</v>
       </c>
       <c r="F17">
-        <v>-4.339454973959095</v>
+        <v>-4.286326802213146</v>
       </c>
       <c r="G17">
-        <v>-9.675676319022065</v>
+        <v>-11.82242936887232</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.523890774723007</v>
       </c>
       <c r="E18">
-        <v>-25.34976105681118</v>
+        <v>-31.69550941952265</v>
       </c>
       <c r="F18">
-        <v>-3.713809783809698</v>
+        <v>-4.308953657820614</v>
       </c>
       <c r="G18">
-        <v>-9.607664471463277</v>
+        <v>-11.81248780061789</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.32227274264358</v>
       </c>
       <c r="E19">
-        <v>-25.50301367417876</v>
+        <v>-32.48850635266484</v>
       </c>
       <c r="F19">
-        <v>-4.035150895071085</v>
+        <v>-4.114282347958313</v>
       </c>
       <c r="G19">
-        <v>-9.63467852306373</v>
+        <v>-11.71746190145865</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.180266846782048</v>
       </c>
       <c r="E20">
-        <v>-27.84438417578659</v>
+        <v>-33.04070394468615</v>
       </c>
       <c r="F20">
-        <v>-3.257279112411431</v>
+        <v>-3.962880809381244</v>
       </c>
       <c r="G20">
-        <v>-9.206734232838762</v>
+        <v>-11.39123081238225</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.106671255201318</v>
       </c>
       <c r="E21">
-        <v>-29.33244073470707</v>
+        <v>-33.33308260475438</v>
       </c>
       <c r="F21">
-        <v>-3.440767462335939</v>
+        <v>-3.636092354079048</v>
       </c>
       <c r="G21">
-        <v>-8.873210011939348</v>
+        <v>-11.33829187866376</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.095806610033679</v>
       </c>
       <c r="E22">
-        <v>-29.25025798841587</v>
+        <v>-34.34121148834195</v>
       </c>
       <c r="F22">
-        <v>-3.049110384087915</v>
+        <v>-3.664545117630405</v>
       </c>
       <c r="G22">
-        <v>-8.506106927635104</v>
+        <v>-11.23440033855035</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.130261794520739</v>
       </c>
       <c r="E23">
-        <v>-27.86247542944723</v>
+        <v>-33.70318346421626</v>
       </c>
       <c r="F23">
-        <v>-3.15617935600196</v>
+        <v>-3.399216553411515</v>
       </c>
       <c r="G23">
-        <v>-8.708718935729578</v>
+        <v>-11.32858204859708</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.202112723728638</v>
       </c>
       <c r="E24">
-        <v>-31.25596667539015</v>
+        <v>-34.33705208496591</v>
       </c>
       <c r="F24">
-        <v>-3.016939079265391</v>
+        <v>-3.326491694017538</v>
       </c>
       <c r="G24">
-        <v>-9.36131684624949</v>
+        <v>-11.27711630764357</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.298241595348631</v>
       </c>
       <c r="E25">
-        <v>-30.98894067705386</v>
+        <v>-34.60456263002102</v>
       </c>
       <c r="F25">
-        <v>-2.936801159983761</v>
+        <v>-3.419912484603058</v>
       </c>
       <c r="G25">
-        <v>-8.374420047173976</v>
+        <v>-11.03333435522272</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.401075540166439</v>
       </c>
       <c r="E26">
-        <v>-29.28994100614508</v>
+        <v>-35.33507115033136</v>
       </c>
       <c r="F26">
-        <v>-2.619405562661909</v>
+        <v>-3.282912941691062</v>
       </c>
       <c r="G26">
-        <v>-9.645609944434403</v>
+        <v>-11.4890143959757</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.497682377030824</v>
       </c>
       <c r="E27">
-        <v>-29.9365436958043</v>
+        <v>-34.30985180583884</v>
       </c>
       <c r="F27">
-        <v>-2.555699967549613</v>
+        <v>-3.140234111865472</v>
       </c>
       <c r="G27">
-        <v>-8.844312259927049</v>
+        <v>-11.63162276617089</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.582225146206001</v>
       </c>
       <c r="E28">
-        <v>-31.79658722361086</v>
+        <v>-35.46430474156226</v>
       </c>
       <c r="F28">
-        <v>-2.443001410766143</v>
+        <v>-3.373024404502398</v>
       </c>
       <c r="G28">
-        <v>-8.313287513245793</v>
+        <v>-11.43432418366694</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.646815909643103</v>
       </c>
       <c r="E29">
-        <v>-30.45072022005722</v>
+        <v>-34.82105538690572</v>
       </c>
       <c r="F29">
-        <v>-2.439414579912021</v>
+        <v>-3.371754517273906</v>
       </c>
       <c r="G29">
-        <v>-7.825117778570403</v>
+        <v>-11.71420101410247</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.681625412284681</v>
       </c>
       <c r="E30">
-        <v>-29.66853501860835</v>
+        <v>-34.88641711649543</v>
       </c>
       <c r="F30">
-        <v>-2.453721313325771</v>
+        <v>-3.01076028680791</v>
       </c>
       <c r="G30">
-        <v>-9.078983591023826</v>
+        <v>-11.54047351583813</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.6900850060954</v>
       </c>
       <c r="E31">
-        <v>-29.86930491373841</v>
+        <v>-34.66989492452968</v>
       </c>
       <c r="F31">
-        <v>-2.301364667133275</v>
+        <v>-3.218783222468533</v>
       </c>
       <c r="G31">
-        <v>-10.03324503217321</v>
+        <v>-11.47860273025469</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.671788352161148</v>
       </c>
       <c r="E32">
-        <v>-29.97517384332673</v>
+        <v>-34.36992427778759</v>
       </c>
       <c r="F32">
-        <v>-1.839693976000637</v>
+        <v>-3.077964077462228</v>
       </c>
       <c r="G32">
-        <v>-9.43922391442516</v>
+        <v>-11.91893177134208</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.623752711633651</v>
       </c>
       <c r="E33">
-        <v>-29.55384009317908</v>
+        <v>-33.52383777961649</v>
       </c>
       <c r="F33">
-        <v>-2.448133975193888</v>
+        <v>-3.194064739168995</v>
       </c>
       <c r="G33">
-        <v>-8.559201456993936</v>
+        <v>-12.13539510197286</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.551386667012621</v>
       </c>
       <c r="E34">
-        <v>-29.77851353835863</v>
+        <v>-33.82768932858315</v>
       </c>
       <c r="F34">
-        <v>-2.431768748784181</v>
+        <v>-3.301348258240365</v>
       </c>
       <c r="G34">
-        <v>-8.701184134082197</v>
+        <v>-11.76173382695532</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.459373496548316</v>
       </c>
       <c r="E35">
-        <v>-28.30003923043838</v>
+        <v>-33.06601358591502</v>
       </c>
       <c r="F35">
-        <v>-2.681965525656133</v>
+        <v>-3.262352862753578</v>
       </c>
       <c r="G35">
-        <v>-10.69902222448496</v>
+        <v>-12.0415477570256</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.348075609149276</v>
       </c>
       <c r="E36">
-        <v>-30.30407691050383</v>
+        <v>-32.83735508360871</v>
       </c>
       <c r="F36">
-        <v>-2.87432486209722</v>
+        <v>-3.013426801477521</v>
       </c>
       <c r="G36">
-        <v>-8.375426453017914</v>
+        <v>-11.94592927021483</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.218798352923289</v>
       </c>
       <c r="E37">
-        <v>-27.27499649643216</v>
+        <v>-32.64400962161422</v>
       </c>
       <c r="F37">
-        <v>-2.35017455960843</v>
+        <v>-3.10122214903063</v>
       </c>
       <c r="G37">
-        <v>-9.537633191125535</v>
+        <v>-12.25695171308382</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.077327564783383</v>
       </c>
       <c r="E38">
-        <v>-28.01268944075566</v>
+        <v>-31.87453358246788</v>
       </c>
       <c r="F38">
-        <v>-2.281669403764313</v>
+        <v>-3.180501051315556</v>
       </c>
       <c r="G38">
-        <v>-8.971798058098843</v>
+        <v>-12.49205010455516</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.924224499939834</v>
       </c>
       <c r="E39">
-        <v>-26.50916814309899</v>
+        <v>-31.89309353318832</v>
       </c>
       <c r="F39">
-        <v>-2.709938664481269</v>
+        <v>-3.012315132422964</v>
       </c>
       <c r="G39">
-        <v>-9.298499244641819</v>
+        <v>-12.1442243269261</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.755794739609318</v>
       </c>
       <c r="E40">
-        <v>-27.10242540894786</v>
+        <v>-31.39250016672141</v>
       </c>
       <c r="F40">
-        <v>-2.605658805612451</v>
+        <v>-3.04538935771454</v>
       </c>
       <c r="G40">
-        <v>-9.859381801541762</v>
+        <v>-12.00284747967152</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.577447422324475</v>
       </c>
       <c r="E41">
-        <v>-26.86699910223709</v>
+        <v>-31.04574359076907</v>
       </c>
       <c r="F41">
-        <v>-2.703464973228391</v>
+        <v>-3.10298574323119</v>
       </c>
       <c r="G41">
-        <v>-8.932942185104416</v>
+        <v>-12.01252089373727</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.388735908683302</v>
       </c>
       <c r="E42">
-        <v>-25.79539912695801</v>
+        <v>-30.99913427204513</v>
       </c>
       <c r="F42">
-        <v>-2.164743688124358</v>
+        <v>-2.982657922667936</v>
       </c>
       <c r="G42">
-        <v>-9.13724257142392</v>
+        <v>-12.17169192326543</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.185802451866404</v>
       </c>
       <c r="E43">
-        <v>-25.92571955195074</v>
+        <v>-30.77457856718977</v>
       </c>
       <c r="F43">
-        <v>-2.665999572334575</v>
+        <v>-3.02828357084673</v>
       </c>
       <c r="G43">
-        <v>-9.045600049805815</v>
+        <v>-12.34457523241725</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.971154645196583</v>
       </c>
       <c r="E44">
-        <v>-25.78069064338109</v>
+        <v>-29.67602285038003</v>
       </c>
       <c r="F44">
-        <v>-2.700023106669759</v>
+        <v>-3.204784641728624</v>
       </c>
       <c r="G44">
-        <v>-9.604330752105231</v>
+        <v>-12.19535901332568</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.747106634482523</v>
       </c>
       <c r="E45">
-        <v>-24.0946673147413</v>
+        <v>-29.31940778651299</v>
       </c>
       <c r="F45">
-        <v>-2.717244864973961</v>
+        <v>-2.947747206844354</v>
       </c>
       <c r="G45">
-        <v>-8.881069247049577</v>
+        <v>-12.25937172187303</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.513412511370935</v>
       </c>
       <c r="E46">
-        <v>-24.15604172296725</v>
+        <v>-29.24138670783484</v>
       </c>
       <c r="F46">
-        <v>-2.553104692476642</v>
+        <v>-3.109360858763135</v>
       </c>
       <c r="G46">
-        <v>-8.988102494879753</v>
+        <v>-12.63588668714542</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.271786238025229</v>
       </c>
       <c r="E47">
-        <v>-22.01028771306876</v>
+        <v>-28.25951844501775</v>
       </c>
       <c r="F47">
-        <v>-2.551144775201618</v>
+        <v>-2.857407942997249</v>
       </c>
       <c r="G47">
-        <v>-9.108900991062219</v>
+        <v>-12.47337531716813</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.02974102025208</v>
       </c>
       <c r="E48">
-        <v>-23.28878913728429</v>
+        <v>-28.41161177303936</v>
       </c>
       <c r="F48">
-        <v>-2.329684891900184</v>
+        <v>-2.869156677871154</v>
       </c>
       <c r="G48">
-        <v>-9.447914096465746</v>
+        <v>-12.64287855932436</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.791601871822318</v>
       </c>
       <c r="E49">
-        <v>-23.31927482430393</v>
+        <v>-27.81379886233879</v>
       </c>
       <c r="F49">
-        <v>-2.649634345924868</v>
+        <v>-2.932343714989297</v>
       </c>
       <c r="G49">
-        <v>-9.059060727968491</v>
+        <v>-12.60418490306136</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.55923255249101</v>
       </c>
       <c r="E50">
-        <v>-22.80450959843002</v>
+        <v>-27.36746793566878</v>
       </c>
       <c r="F50">
-        <v>-2.961526270222521</v>
+        <v>-3.015645997749621</v>
       </c>
       <c r="G50">
-        <v>-9.513856853062489</v>
+        <v>-12.72288120282639</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.3431510541916</v>
       </c>
       <c r="E51">
-        <v>-23.64634838798193</v>
+        <v>-26.53251242660853</v>
       </c>
       <c r="F51">
-        <v>-2.335644166995924</v>
+        <v>-3.020714777887351</v>
       </c>
       <c r="G51">
-        <v>-10.7913003708466</v>
+        <v>-12.79568672032604</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.150224344379454</v>
       </c>
       <c r="E52">
-        <v>-22.62780854265072</v>
+        <v>-26.17426937633574</v>
       </c>
       <c r="F52">
-        <v>-2.415879833631084</v>
+        <v>-2.922168049813308</v>
       </c>
       <c r="G52">
-        <v>-9.945836698299829</v>
+        <v>-12.98384157605052</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.985465153108224</v>
       </c>
       <c r="E53">
-        <v>-20.21202615614886</v>
+        <v>-25.7858304613798</v>
       </c>
       <c r="F53">
-        <v>-2.419670442866294</v>
+        <v>-3.111278529300616</v>
       </c>
       <c r="G53">
-        <v>-9.522063695454342</v>
+        <v>-12.77969678537136</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.856890501695298</v>
       </c>
       <c r="E54">
-        <v>-21.21097129444887</v>
+        <v>-25.48879426579468</v>
       </c>
       <c r="F54">
-        <v>-2.489724645753646</v>
+        <v>-2.931360442882174</v>
       </c>
       <c r="G54">
-        <v>-10.04305417860607</v>
+        <v>-12.78014370901916</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.772412186421151</v>
       </c>
       <c r="E55">
-        <v>-21.68280205825606</v>
+        <v>-25.24633071047599</v>
       </c>
       <c r="F55">
-        <v>-2.815990401224676</v>
+        <v>-3.392846408083987</v>
       </c>
       <c r="G55">
-        <v>-10.28399568295422</v>
+        <v>-13.01860230421286</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.735276310909669</v>
       </c>
       <c r="E56">
-        <v>-18.9274882760811</v>
+        <v>-24.99682084960137</v>
       </c>
       <c r="F56">
-        <v>-2.210257506703774</v>
+        <v>-2.885670182045962</v>
       </c>
       <c r="G56">
-        <v>-10.55261003746515</v>
+        <v>-12.76477284608032</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.744059936213284</v>
       </c>
       <c r="E57">
-        <v>-21.56727162937238</v>
+        <v>-25.47211136755042</v>
       </c>
       <c r="F57">
-        <v>-2.822156768171115</v>
+        <v>-3.255707699448321</v>
       </c>
       <c r="G57">
-        <v>-10.07497776924126</v>
+        <v>-12.80972343341255</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.801324823112523</v>
       </c>
       <c r="E58">
-        <v>-19.11960878585651</v>
+        <v>-24.78297725001116</v>
       </c>
       <c r="F58">
-        <v>-3.098017195549198</v>
+        <v>-3.235021708665611</v>
       </c>
       <c r="G58">
-        <v>-10.46994240480401</v>
+        <v>-13.06218563623737</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.903238593214487</v>
       </c>
       <c r="E59">
-        <v>-19.6637638080402</v>
+        <v>-24.74197644634571</v>
       </c>
       <c r="F59">
-        <v>-2.870121725895415</v>
+        <v>-3.189796990309772</v>
       </c>
       <c r="G59">
-        <v>-10.30226658378546</v>
+        <v>-13.64239846854112</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.040328712936993</v>
       </c>
       <c r="E60">
-        <v>-18.90191598335978</v>
+        <v>-24.40394397556915</v>
       </c>
       <c r="F60">
-        <v>-3.020104271111488</v>
+        <v>-3.12507167492463</v>
       </c>
       <c r="G60">
-        <v>-10.70267375621477</v>
+        <v>-13.60545609086839</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.206262508945443</v>
       </c>
       <c r="E61">
-        <v>-18.34933799952182</v>
+        <v>-24.54034161268018</v>
       </c>
       <c r="F61">
-        <v>-3.040021536944399</v>
+        <v>-3.202161202163958</v>
       </c>
       <c r="G61">
-        <v>-10.10845400573437</v>
+        <v>-13.4933047396345</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.392877899920276</v>
       </c>
       <c r="E62">
-        <v>-17.65054011845019</v>
+        <v>-24.4805476418829</v>
       </c>
       <c r="F62">
-        <v>-2.958198718365475</v>
+        <v>-3.215853286964831</v>
       </c>
       <c r="G62">
-        <v>-10.41705975035969</v>
+        <v>-14.14348926245628</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.589458822933947</v>
       </c>
       <c r="E63">
-        <v>-20.29440815529639</v>
+        <v>-24.04469107559265</v>
       </c>
       <c r="F63">
-        <v>-3.162580979290795</v>
+        <v>-3.199510426474999</v>
       </c>
       <c r="G63">
-        <v>-9.692467405997249</v>
+        <v>-13.61627329841796</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.785958456414107</v>
       </c>
       <c r="E64">
-        <v>-18.96808151708585</v>
+        <v>-24.10469788466829</v>
       </c>
       <c r="F64">
-        <v>-3.243372480453233</v>
+        <v>-3.223799815459886</v>
       </c>
       <c r="G64">
-        <v>-10.95821476639112</v>
+        <v>-13.5284660438071</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.976647298865433</v>
       </c>
       <c r="E65">
-        <v>-16.33586071538738</v>
+        <v>-23.25225793746442</v>
       </c>
       <c r="F65">
-        <v>-3.283209497221264</v>
+        <v>-3.163515377721152</v>
       </c>
       <c r="G65">
-        <v>-10.8940696360222</v>
+        <v>-13.43802856076529</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.154181275695294</v>
       </c>
       <c r="E66">
-        <v>-19.53014665396988</v>
+        <v>-23.20307418126711</v>
       </c>
       <c r="F66">
-        <v>-3.113115019832622</v>
+        <v>-3.243949852532984</v>
       </c>
       <c r="G66">
-        <v>-10.89267589635016</v>
+        <v>-13.60443147702398</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.30957071552101</v>
       </c>
       <c r="E67">
-        <v>-16.97068484415265</v>
+        <v>-23.3756996104395</v>
       </c>
       <c r="F67">
-        <v>-2.910040751036323</v>
+        <v>-3.400979319244673</v>
       </c>
       <c r="G67">
-        <v>-11.13702395205823</v>
+        <v>-13.2231079443558</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.440975619605325</v>
       </c>
       <c r="E68">
-        <v>-19.15661094697318</v>
+        <v>-22.80707271471836</v>
       </c>
       <c r="F68">
-        <v>-2.963240162378913</v>
+        <v>-3.384130326271731</v>
       </c>
       <c r="G68">
-        <v>-10.93694782184684</v>
+        <v>-13.79319712840046</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.545520419613601</v>
       </c>
       <c r="E69">
-        <v>-18.26727752202883</v>
+        <v>-23.27608223921877</v>
       </c>
       <c r="F69">
-        <v>-2.948373452600871</v>
+        <v>-3.24604645042947</v>
       </c>
       <c r="G69">
-        <v>-10.04718904998462</v>
+        <v>-13.55776437182965</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.619203681793617</v>
       </c>
       <c r="E70">
-        <v>-17.33609646877959</v>
+        <v>-23.18245151063618</v>
       </c>
       <c r="F70">
-        <v>-3.306239767753896</v>
+        <v>-3.432309002785953</v>
       </c>
       <c r="G70">
-        <v>-11.43328467236761</v>
+        <v>-13.34160892193401</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.661670387110829</v>
       </c>
       <c r="E71">
-        <v>-16.86303848851632</v>
+        <v>-23.10338888293626</v>
       </c>
       <c r="F71">
-        <v>-3.614227596482155</v>
+        <v>-3.14983240496171</v>
       </c>
       <c r="G71">
-        <v>-10.21248127821489</v>
+        <v>-13.58863851952889</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.673493616455998</v>
       </c>
       <c r="E72">
-        <v>-19.82296684025386</v>
+        <v>-23.1100819675196</v>
       </c>
       <c r="F72">
-        <v>-3.455059285136438</v>
+        <v>-3.412780241264954</v>
       </c>
       <c r="G72">
-        <v>-10.09174899294321</v>
+        <v>-13.24950292394041</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.653158791650567</v>
       </c>
       <c r="E73">
-        <v>-18.3348604681193</v>
+        <v>-22.94212539504911</v>
       </c>
       <c r="F73">
-        <v>-2.904354837183508</v>
+        <v>-3.733205178178845</v>
       </c>
       <c r="G73">
-        <v>-9.915740528802315</v>
+        <v>-13.52493038117116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.599164610704084</v>
       </c>
       <c r="E74">
-        <v>-17.25932524892755</v>
+        <v>-23.69430492772316</v>
       </c>
       <c r="F74">
-        <v>-3.302729146700832</v>
+        <v>-3.673759048251744</v>
       </c>
       <c r="G74">
-        <v>-10.45957708672055</v>
+        <v>-12.85270093560337</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.513091517906564</v>
       </c>
       <c r="E75">
-        <v>-19.16431388126023</v>
+        <v>-24.05794139053909</v>
       </c>
       <c r="F75">
-        <v>-3.180334549467594</v>
+        <v>-3.477788858301854</v>
       </c>
       <c r="G75">
-        <v>-10.62808716521499</v>
+        <v>-13.00402597220345</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.394408689339446</v>
       </c>
       <c r="E76">
-        <v>-20.72180100366631</v>
+        <v>-24.24456433286919</v>
       </c>
       <c r="F76">
-        <v>-3.340254190047649</v>
+        <v>-3.642722606771055</v>
       </c>
       <c r="G76">
-        <v>-10.52550660113514</v>
+        <v>-12.88416104986306</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.24139911690952</v>
       </c>
       <c r="E77">
-        <v>-21.02362379627754</v>
+        <v>-23.75049423321033</v>
       </c>
       <c r="F77">
-        <v>-4.003898249698265</v>
+        <v>-3.631352435800229</v>
       </c>
       <c r="G77">
-        <v>-10.32073942789459</v>
+        <v>-12.92225218683791</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.057967871589129</v>
       </c>
       <c r="E78">
-        <v>-20.80834014195289</v>
+        <v>-24.85605323507293</v>
       </c>
       <c r="F78">
-        <v>-3.955427159490855</v>
+        <v>-3.501341000298249</v>
       </c>
       <c r="G78">
-        <v>-8.704699933444903</v>
+        <v>-12.73525933259772</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.845611201021931</v>
       </c>
       <c r="E79">
-        <v>-20.87287995351021</v>
+        <v>-25.09593103173324</v>
       </c>
       <c r="F79">
-        <v>-3.828993442801566</v>
+        <v>-3.826794127347133</v>
       </c>
       <c r="G79">
-        <v>-10.06107347797632</v>
+        <v>-12.96177347948573</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.605049208163681</v>
       </c>
       <c r="E80">
-        <v>-20.54422595240354</v>
+        <v>-25.52518055444631</v>
       </c>
       <c r="F80">
-        <v>-3.783715708931948</v>
+        <v>-3.890752374517283</v>
       </c>
       <c r="G80">
-        <v>-9.32779757266437</v>
+        <v>-12.95861521904127</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.341653303413585</v>
       </c>
       <c r="E81">
-        <v>-21.71550216906545</v>
+        <v>-25.84938759407745</v>
       </c>
       <c r="F81">
-        <v>-3.87402432318515</v>
+        <v>-3.763493603894807</v>
       </c>
       <c r="G81">
-        <v>-9.091209435700355</v>
+        <v>-12.80104318300858</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.060658516652238</v>
       </c>
       <c r="E82">
-        <v>-22.1234271076764</v>
+        <v>-26.3447483088285</v>
       </c>
       <c r="F82">
-        <v>-3.665796780776036</v>
+        <v>-4.045951977636188</v>
       </c>
       <c r="G82">
-        <v>-9.040018470026604</v>
+        <v>-12.35537092142081</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.766250321689967</v>
       </c>
       <c r="E83">
-        <v>-22.94905396028085</v>
+        <v>-27.06105327041378</v>
       </c>
       <c r="F83">
-        <v>-3.691730479055479</v>
+        <v>-4.244531524904896</v>
       </c>
       <c r="G83">
-        <v>-9.147866112059441</v>
+        <v>-12.10054829962649</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.464671963318224</v>
       </c>
       <c r="E84">
-        <v>-23.68038439862358</v>
+        <v>-27.78860696143411</v>
       </c>
       <c r="F84">
-        <v>-4.134276651959684</v>
+        <v>-4.152352457056173</v>
       </c>
       <c r="G84">
-        <v>-8.799593410782574</v>
+        <v>-12.16398166270447</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.165281363616891</v>
       </c>
       <c r="E85">
-        <v>-23.6456827023028</v>
+        <v>-27.9605168917133</v>
       </c>
       <c r="F85">
-        <v>-3.439930811259111</v>
+        <v>-4.049183438874508</v>
       </c>
       <c r="G85">
-        <v>-8.146340012245886</v>
+        <v>-11.91483662651</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.8765421457942735</v>
       </c>
       <c r="E86">
-        <v>-23.78281848067708</v>
+        <v>-29.67031244465636</v>
       </c>
       <c r="F86">
-        <v>-3.654494535932239</v>
+        <v>-4.313117860754486</v>
       </c>
       <c r="G86">
-        <v>-8.392340030178049</v>
+        <v>-11.7144062679259</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.6062525555569801</v>
       </c>
       <c r="E87">
-        <v>-26.56308415463431</v>
+        <v>-29.89366131118867</v>
       </c>
       <c r="F87">
-        <v>-4.818129562768997</v>
+        <v>-4.331461228522079</v>
       </c>
       <c r="G87">
-        <v>-7.212842312718815</v>
+        <v>-11.91222129553397</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.3679801183687808</v>
       </c>
       <c r="E88">
-        <v>-27.95537254524058</v>
+        <v>-30.74942289407716</v>
       </c>
       <c r="F88">
-        <v>-4.174469038343517</v>
+        <v>-4.300394137447486</v>
       </c>
       <c r="G88">
-        <v>-7.404241503071779</v>
+        <v>-11.78709591633168</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.1733824922140592</v>
       </c>
       <c r="E89">
-        <v>-29.69228460054158</v>
+        <v>-31.90142139688842</v>
       </c>
       <c r="F89">
-        <v>-4.06213247811507</v>
+        <v>-4.397591455022369</v>
       </c>
       <c r="G89">
-        <v>-7.999811956132205</v>
+        <v>-11.82172422267245</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.03249746912800148</v>
       </c>
       <c r="E90">
-        <v>-30.37917712344704</v>
+        <v>-33.64204000816469</v>
       </c>
       <c r="F90">
-        <v>-3.975144788779691</v>
+        <v>-4.595592801843924</v>
       </c>
       <c r="G90">
-        <v>-6.785543578874004</v>
+        <v>-11.9977790344509</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.04314491280505678</v>
       </c>
       <c r="E91">
-        <v>-30.33144927164319</v>
+        <v>-34.04649160721176</v>
       </c>
       <c r="F91">
-        <v>-3.750441847096297</v>
+        <v>-4.783337303484015</v>
       </c>
       <c r="G91">
-        <v>-7.330419648091571</v>
+        <v>-11.79766317769303</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.03975158608556756</v>
       </c>
       <c r="E92">
-        <v>-33.09236930463966</v>
+        <v>-35.17707042796674</v>
       </c>
       <c r="F92">
-        <v>-4.243712269543527</v>
+        <v>-4.574285535509115</v>
       </c>
       <c r="G92">
-        <v>-7.79229040900299</v>
+        <v>-12.20684329580141</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.05317697001558908</v>
       </c>
       <c r="E93">
-        <v>-34.40383349115702</v>
+        <v>-36.83372660266679</v>
       </c>
       <c r="F93">
-        <v>-4.34630971421726</v>
+        <v>-4.746691986318971</v>
       </c>
       <c r="G93">
-        <v>-8.496469929570285</v>
+        <v>-12.25251889260674</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.2395573848898319</v>
       </c>
       <c r="E94">
-        <v>-35.79969031928134</v>
+        <v>-38.52495994065242</v>
       </c>
       <c r="F94">
-        <v>-3.999790375747782</v>
+        <v>-4.641026268785268</v>
       </c>
       <c r="G94">
-        <v>-8.940963636946071</v>
+        <v>-12.04880116230214</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.5246053694375311</v>
       </c>
       <c r="E95">
-        <v>-36.80498664237712</v>
+        <v>-40.33045120632557</v>
       </c>
       <c r="F95">
-        <v>-4.226845880855127</v>
+        <v>-4.915752661188919</v>
       </c>
       <c r="G95">
-        <v>-8.270700655428609</v>
+        <v>-12.65699472550381</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.9124628466911908</v>
       </c>
       <c r="E96">
-        <v>-38.30133257296863</v>
+        <v>-41.87453857414295</v>
       </c>
       <c r="F96">
-        <v>-4.036570716799483</v>
+        <v>-4.918545087703756</v>
       </c>
       <c r="G96">
-        <v>-8.473865524628142</v>
+        <v>-12.3822525511997</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.385982718774468</v>
       </c>
       <c r="E97">
-        <v>-40.79447488094353</v>
+        <v>-43.02643065781503</v>
       </c>
       <c r="F97">
-        <v>-4.190545992897049</v>
+        <v>-5.082527042027141</v>
       </c>
       <c r="G97">
-        <v>-8.92539083072934</v>
+        <v>-12.87956932320009</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.949637220228243</v>
       </c>
       <c r="E98">
-        <v>-42.18365220990653</v>
+        <v>-44.73934859358639</v>
       </c>
       <c r="F98">
-        <v>-4.659594124119019</v>
+        <v>-5.230367429139574</v>
       </c>
       <c r="G98">
-        <v>-9.656279832707474</v>
+        <v>-12.84964199152508</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.567451995312014</v>
       </c>
       <c r="E99">
-        <v>-45.04609610168096</v>
+        <v>-46.38677800249581</v>
       </c>
       <c r="F99">
-        <v>-4.401029179743987</v>
+        <v>-5.113615670654206</v>
       </c>
       <c r="G99">
-        <v>-8.497549167416087</v>
+        <v>-13.32854219869051</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.258306888801199</v>
       </c>
       <c r="E100">
-        <v>-46.32876145774654</v>
+        <v>-48.14662677864565</v>
       </c>
       <c r="F100">
-        <v>-4.280780882451403</v>
+        <v>-5.377024907600809</v>
       </c>
       <c r="G100">
-        <v>-10.6577529637924</v>
+        <v>-13.22916293214713</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.94232136092745</v>
       </c>
       <c r="E101">
-        <v>-47.19611140562066</v>
+        <v>-49.63167756294354</v>
       </c>
       <c r="F101">
-        <v>-4.774077812655522</v>
+        <v>-5.732349791562046</v>
       </c>
       <c r="G101">
-        <v>-10.31059922690781</v>
+        <v>-13.80419310540915</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.700991831175379</v>
       </c>
       <c r="E102">
-        <v>-50.62530061216605</v>
+        <v>-52.4140240707073</v>
       </c>
       <c r="F102">
-        <v>-4.588160689506006</v>
+        <v>-5.589472981927187</v>
       </c>
       <c r="G102">
-        <v>-10.00718110714252</v>
+        <v>-14.16077527598959</v>
       </c>
     </row>
   </sheetData>
